--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125026219</v>
       </c>
       <c r="B2" t="n">
-        <v>56836</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125026219</v>
       </c>
       <c r="B2" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125026219</v>
       </c>
       <c r="B2" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125026219</v>
       </c>
       <c r="B2" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125026219</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>56931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125080961</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>125271336</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>57044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>125270925</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>57044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>125283496</v>
       </c>
       <c r="B6" t="n">
-        <v>56843</v>
+        <v>57044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125080961</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>125271336</v>
       </c>
       <c r="B4" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>125270925</v>
       </c>
       <c r="B5" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>125283496</v>
       </c>
       <c r="B6" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125080961</v>
       </c>
       <c r="B3" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>125271336</v>
       </c>
       <c r="B4" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>125270925</v>
       </c>
       <c r="B5" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>125283496</v>
       </c>
       <c r="B6" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Markus Nyberg</t>
+          <t>Markus Nyberg, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Nyberg, Pia Hagfors</t>
+          <t>Pia Hagfors, Markus Nyberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125026219</v>
+        <v>125271374</v>
       </c>
       <c r="B2" t="n">
-        <v>56931</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,47 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hjortronmossen, Hjortronmossen, Vstm</t>
+          <t>Åkerbo, Kolsva, Vstm, Åkerbo, Kolsva, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555797</v>
+        <v>555937</v>
       </c>
       <c r="R2" t="n">
-        <v>6615644</v>
+        <v>6615269</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +748,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökt på tallraka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +779,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Nyberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Nyberg</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125080961</v>
+        <v>125024997</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,14 +846,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hjortronmossen, Musseludden, Vstm</t>
+          <t>Hjortronmossen, Hjortronmossen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555887</v>
+        <v>555744</v>
       </c>
       <c r="R3" t="n">
-        <v>6615722</v>
+        <v>6615537</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -872,22 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125271336</v>
+        <v>125025072</v>
       </c>
       <c r="B4" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555952</v>
+        <v>555772</v>
       </c>
       <c r="R4" t="n">
-        <v>6615288</v>
+        <v>6615506</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -999,27 +1007,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spelspillning</t>
+          <t>Spillning vid tjäderspel</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125270925</v>
+        <v>125026219</v>
       </c>
       <c r="B5" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,26 +1088,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åkerbo, Åkerbo, Vstm</t>
+          <t>Hjortronmossen, Hjortronmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555819</v>
+        <v>555797</v>
       </c>
       <c r="R5" t="n">
-        <v>6615360</v>
+        <v>6615644</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1126,27 +1129,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:55</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125283496</v>
+        <v>125080961</v>
       </c>
       <c r="B6" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,21 +1215,16 @@
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hjortronmosseskogen, Kolsva, Vstm</t>
+          <t>Hjortronmossen, Musseludden, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555936</v>
+        <v>555887</v>
       </c>
       <c r="R6" t="n">
-        <v>6615295</v>
+        <v>6615722</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1258,17 +1251,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillningshög.</t>
+          <t>Spillning efter tjäderspel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,33 +1282,1539 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gran/tallskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125270925</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åkerbo, Åkerbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>555819</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6615360</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125271336</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hjortronmossen, Hjortronmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>555952</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6615288</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125283167</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hjortronmosseskogen, Kolsva, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>555752</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6615466</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Pia Hagfors, Markus Nyberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Skogsprojektet Köping</t>
-        </is>
-      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skogsprojektet, Tjäderinventering Västmanland</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125283188</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hjortronmosseskogen, Kolsva, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>555737</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6615467</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Skogsprojektet, Tjäderinventering Västmanland</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125283223</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hjortronmosseskogen, Kolsva, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>555735</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6615469</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillningshög på häll</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Skogsprojektet, Tjäderinventering Västmanland</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125283496</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hjortronmosseskogen, Kolsva, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>555936</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6615295</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillningshög.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gran/tallskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pia Hagfors, Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Tjäderinventering Västmanland</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125998238</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hjortronmossen (söder Täkten), Odensvi sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>556094</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6615610</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132782382</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Spel, Nybyn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>555970</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6615755</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spelspillning på ej trafikerad grusväg som går mellan hällmarker nära myr.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132782594</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hjortronmossen, Hjortronmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>556030</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6615746</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spelspillning på häll nära myr med större tallar.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127820505</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hjortronmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>555755</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6615474</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133325609</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hjortronmossen, Kolsva, Köping, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>556019</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6615764</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127128691</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Åkerbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>555751</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6615525</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Markus Nyberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35206-2025 artfynd.xlsx
+++ b/artfynd/A 35206-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271374</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125024997</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1051,6 +1066,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125025072</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1168,6 +1188,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125026219</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1295,6 +1320,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125080961</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1422,6 +1452,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125270925</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1549,6 +1584,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271336</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1675,6 +1715,11 @@
           <t>Skogsprojektet, Tjäderinventering Västmanland</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283167</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1801,6 +1846,11 @@
           <t>Skogsprojektet, Tjäderinventering Västmanland</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283188</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1932,6 +1982,11 @@
           <t>Skogsprojektet, Tjäderinventering Västmanland</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283223</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2068,6 +2123,11 @@
           <t>Tjäderinventering Västmanland</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283496</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2195,6 +2255,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125998238</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2327,6 +2392,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132782382</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2459,6 +2529,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132782594</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2566,6 +2641,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127820505</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2689,6 +2769,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133325609</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2815,8 +2900,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128691</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>